--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3018,6 +3018,788 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125543534</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98297</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>697161</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6364900</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125543543</v>
+      </c>
+      <c r="B23" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>697093</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6364942</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125543554</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>697002</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6364909</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125543567</v>
+      </c>
+      <c r="B25" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696924</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6364966</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125543549</v>
+      </c>
+      <c r="B26" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>697030</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6364977</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125543512</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98247</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>697146</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6364968</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125543515</v>
+      </c>
+      <c r="B28" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>697152</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6364941</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med kontinuitet.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3020,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125543534</v>
+        <v>125543543</v>
       </c>
       <c r="B22" t="n">
-        <v>98297</v>
+        <v>109082</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,20 +3032,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3053,31 +3053,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697161</v>
+        <v>697093</v>
       </c>
       <c r="R22" t="n">
-        <v>6364900</v>
+        <v>6364942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3141,10 +3127,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125543543</v>
+        <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>109082</v>
+        <v>98297</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3153,20 +3139,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3174,17 +3160,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697093</v>
+        <v>697161</v>
       </c>
       <c r="R23" t="n">
-        <v>6364942</v>
+        <v>6364900</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543554</v>
+        <v>125543567</v>
       </c>
       <c r="B24" t="n">
         <v>109082</v>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697002</v>
+        <v>696924</v>
       </c>
       <c r="R24" t="n">
-        <v>6364909</v>
+        <v>6364966</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3326,6 +3326,11 @@
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3337,7 +3342,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3355,7 +3360,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543567</v>
+        <v>125543515</v>
       </c>
       <c r="B25" t="n">
         <v>109082</v>
@@ -3395,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696924</v>
+        <v>697152</v>
       </c>
       <c r="R25" t="n">
-        <v>6364966</v>
+        <v>6364941</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3433,11 +3438,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543549</v>
+        <v>125543554</v>
       </c>
       <c r="B26" t="n">
         <v>109082</v>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697030</v>
+        <v>697002</v>
       </c>
       <c r="R26" t="n">
-        <v>6364977</v>
+        <v>6364909</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125543512</v>
+        <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>98247</v>
+        <v>109082</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,52 +3586,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697146</v>
+        <v>697030</v>
       </c>
       <c r="R27" t="n">
-        <v>6364968</v>
+        <v>6364977</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3695,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B28" t="n">
-        <v>109082</v>
+        <v>98247</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,38 +3693,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R28" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3799,6 +3799,117 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125628684</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58345</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>697149</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6364892</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3020,15 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125543543</v>
+        <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,13 +3055,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697093</v>
+        <v>697002</v>
       </c>
       <c r="R22" t="n">
-        <v>6364942</v>
+        <v>6364909</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3130,12 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98297</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,15 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543567</v>
+        <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3288,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696924</v>
+        <v>697152</v>
       </c>
       <c r="R24" t="n">
-        <v>6364966</v>
+        <v>6364941</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3326,11 +3311,6 @@
           <t>2025-05-23</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3322,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
+          <t>Kalkbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3360,50 +3340,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98302</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R25" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3467,15 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125543554</v>
+        <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,10 +3491,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697002</v>
+        <v>696924</v>
       </c>
       <c r="R26" t="n">
-        <v>6364909</v>
+        <v>6364966</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3545,6 +3529,11 @@
           <t>2025-05-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3556,7 +3545,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med kontinuitet.</t>
+          <t>Kalkbarrskog med kontinuitet. Något tuvigt, troligen vinterfuktigt område.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3577,12 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3681,67 +3665,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125543512</v>
+        <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>98247</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697146</v>
+        <v>697093</v>
       </c>
       <c r="R28" t="n">
-        <v>6364968</v>
+        <v>6364942</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3805,12 +3770,7 @@
         <v>125628684</v>
       </c>
       <c r="B29" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>98302</v>
+        <v>98309</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>98362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>98309</v>
+        <v>98312</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>125628684</v>
       </c>
       <c r="B29" t="n">
-        <v>58365</v>
+        <v>58366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98362</v>
+        <v>98366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98367</v>
+        <v>98369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>125628684</v>
       </c>
       <c r="B29" t="n">
-        <v>58366</v>
+        <v>58367</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,6 +3870,117 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126202334</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>696928</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6365068</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flyger i skogen, på båda sidor om stigen</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av löv, gran</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3023,7 +3023,7 @@
         <v>125543554</v>
       </c>
       <c r="B22" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125543534</v>
       </c>
       <c r="B23" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3238,45 +3238,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B24" t="n">
-        <v>109154</v>
+        <v>98321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R24" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3340,59 +3354,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543512</v>
+        <v>125543515</v>
       </c>
       <c r="B25" t="n">
-        <v>98319</v>
+        <v>109156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697146</v>
+        <v>697152</v>
       </c>
       <c r="R25" t="n">
-        <v>6364968</v>
+        <v>6364941</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3459,7 +3459,7 @@
         <v>125543567</v>
       </c>
       <c r="B26" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>125543549</v>
       </c>
       <c r="B27" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>125543543</v>
       </c>
       <c r="B28" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3982,6 +3982,324 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126243284</v>
+      </c>
+      <c r="B31" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>697024</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6364989</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126243286</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>696958</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6365064</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126243285</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43227</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Klinte Hunninge 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>697017</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6364987</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Klinte</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gun Ingmansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3238,59 +3238,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125543512</v>
+        <v>125543515</v>
       </c>
       <c r="B24" t="n">
-        <v>98321</v>
+        <v>109156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697146</v>
+        <v>697152</v>
       </c>
       <c r="R24" t="n">
-        <v>6364968</v>
+        <v>6364941</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3354,45 +3340,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125543515</v>
+        <v>125543512</v>
       </c>
       <c r="B25" t="n">
-        <v>109156</v>
+        <v>98321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klinte Hunninge 1:15., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697152</v>
+        <v>697146</v>
       </c>
       <c r="R25" t="n">
-        <v>6364941</v>
+        <v>6364968</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3770,7 +3770,7 @@
         <v>125628684</v>
       </c>
       <c r="B29" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 3475-2025 artfynd.xlsx
+++ b/artfynd/A 3475-2025 artfynd.xlsx
@@ -3876,7 +3876,7 @@
         <v>126202334</v>
       </c>
       <c r="B30" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>126243284</v>
       </c>
       <c r="B31" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>126243286</v>
       </c>
       <c r="B32" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>126243285</v>
       </c>
       <c r="B33" t="n">
-        <v>43227</v>
+        <v>43228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
